--- a/scripts/games-template.xlsx
+++ b/scripts/games-template.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -22,8 +22,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1E1E4E"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -33,6 +39,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E1E4E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5D96FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8ED62"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -49,13 +67,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -67,28 +91,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="22" customWidth="1"/>
-    <col min="15" max="15" width="36" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="30" customWidth="1"/>
-    <col min="18" max="18" width="40" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="24" customWidth="1"/>
-    <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="34" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="32" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="30" customWidth="1"/>
+    <col min="19" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="34" customWidth="1"/>
+    <col min="22" max="22" width="30" customWidth="1"/>
+    <col min="23" max="23" width="30" customWidth="1"/>
+    <col min="24" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="18" customWidth="1"/>
+    <col min="26" max="26" width="11" customWidth="1"/>
+    <col min="27" max="27" width="28" customWidth="1"/>
+    <col min="28" max="28" width="12" customWidth="1"/>
+    <col min="29" max="29" width="30" customWidth="1"/>
+    <col min="30" max="30" width="11" customWidth="1"/>
+    <col min="31" max="31" width="12" customWidth="1"/>
+    <col min="32" max="32" width="28" customWidth="1"/>
+    <col min="33" max="33" width="30" customWidth="1"/>
+    <col min="34" max="34" width="30" customWidth="1"/>
+    <col min="35" max="35" width="18" customWidth="1"/>
+    <col min="36" max="36" width="18" customWidth="1"/>
+    <col min="37" max="37" width="11" customWidth="1"/>
+    <col min="38" max="38" width="28" customWidth="1"/>
+    <col min="39" max="39" width="12" customWidth="1"/>
+    <col min="40" max="40" width="30" customWidth="1"/>
+    <col min="41" max="41" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -159,7 +202,7 @@
       </c>
       <c r="N1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Platforms *</t>
+          <t xml:space="preserve">Platforms</t>
         </is>
       </c>
       <c r="O1" t="inlineStr" s="1">
@@ -174,32 +217,127 @@
       </c>
       <c r="Q1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Partner</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">On Teachers page *</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Teacher grades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Teacher moments</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Teacher URL</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Teacher subtitle</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Teacher image file</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Teacher icon file</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Teacher minutes</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Teacher skills</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Teacher feels like</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Teacher badges</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Teacher featured</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">On Parents page *</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr" s="4">
+        <is>
           <t xml:space="preserve">When (parents)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Teacher moments</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Show on *</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Partner</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Featured</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Notes</t>
+      <c r="AG1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">Parent URL</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">Parent subtitle</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">Parent image file</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">Parent icon file</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">Parent minutes</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">Parent skills</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">Parent feels like</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">Parent badges</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">Parent featured</t>
         </is>
       </c>
     </row>
@@ -231,7 +369,7 @@
       </c>
       <c r="F2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Twelve Set cards laid out in a grid</t>
+          <t xml:space="preserve">Twelve Set cards in a grid</t>
         </is>
       </c>
       <c r="G2" s="2">
@@ -280,32 +418,75 @@
       </c>
       <c r="Q2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Set Enterprises</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EXAMPLE ROW: overwrite or delete</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2-3, 4-5</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Morning warm-up, The last 10 minutes</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://www.setgame.com/teachers</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Project it, race the class</t>
+        </is>
+      </c>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Players, Minutes</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Car or waiting, Free time</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Morning warm-up, The last 10 minutes</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Both</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Set Enterprises</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EXAMPLE ROW: overwrite or delete</t>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="2"/>
+      <c r="AN2" s="2"/>
+      <c r="AO2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
@@ -386,32 +567,79 @@
       </c>
       <c r="Q3" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Art of Problem Solving</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EXAMPLE ROW: overwrite or delete</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2-3, 4-5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Morning warm-up, Early finishers</t>
+        </is>
+      </c>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Car or waiting, Free time</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Morning warm-up, Early finishers</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Both</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Art of Problem Solving</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Yes</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EXAMPLE ROW: overwrite or delete</t>
+      <c r="AG3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">https://beastacademy.com/parents</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A fresh puzzle every day, free</t>
+        </is>
+      </c>
+      <c r="AI3" s="2"/>
+      <c r="AJ3" s="2"/>
+      <c r="AK3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="AL3" s="2"/>
+      <c r="AM3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A game</t>
+        </is>
+      </c>
+      <c r="AN3" s="2"/>
+      <c r="AO3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
     </row>
@@ -486,35 +714,62 @@
           <t xml:space="preserve">Math</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Weekend</t>
-        </is>
-      </c>
+      <c r="Q4" s="2"/>
       <c r="R4" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">EXAMPLE ROW: overwrite or delete</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">K-1, 2-3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Cover or sub day</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Both</t>
-        </is>
-      </c>
-      <c r="T4" s="2"/>
-      <c r="U4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">EXAMPLE ROW: overwrite or delete</t>
-        </is>
-      </c>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="15">
     <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Enter a whole number from 3 to 14" sqref="G2:G500">
       <formula1>3</formula1>
       <formula2>14</formula2>
@@ -539,10 +794,30 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: A game, Math" sqref="P2:P500">
       <formula1>"A game,Math"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Both, Teachers, Parents" sqref="S2:S500">
-      <formula1>"Both,Teachers,Parents"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Yes, No" sqref="S2:S500">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Yes, No" sqref="U2:U500">
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Enter a whole number from 1 to 120" sqref="Z2:Z500">
+      <formula1>1</formula1>
+      <formula2>120</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: A game, Math" sqref="AB2:AB500">
+      <formula1>"A game,Math"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Yes, No" sqref="AD2:AD500">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Yes, No" sqref="AE2:AE500">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Enter a whole number from 1 to 120" sqref="AK2:AK500">
+      <formula1>1</formula1>
+      <formula2>120</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: A game, Math" sqref="AM2:AM500">
+      <formula1>"A game,Math"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Yes, No" sqref="AO2:AO500">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -554,10 +829,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -568,20 +844,25 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Section</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Required?</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">What to enter</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Allowed values</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Shows on the site as</t>
         </is>
@@ -595,20 +876,25 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="2">
+      <c r="D2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">The game's name</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="2">
+      <c r="E2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Free text</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr" s="2">
+      <c r="F2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Card title</t>
         </is>
@@ -622,20 +908,25 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr" s="2">
+      <c r="D3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">One short line, max ~50 characters</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr" s="2">
+      <c r="E3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Free text</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr" s="2">
+      <c r="F3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Line under the name</t>
         </is>
@@ -649,22 +940,27 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Where "Open game" / "Play" takes them: the game's own website</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Where "Open game" / "Play" goes: the game's own website</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Full link starting https://</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">The button on the card</t>
+      <c r="F4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Button on the card</t>
         </is>
       </c>
     </row>
@@ -676,20 +972,25 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">File name of the image you send with this sheet (or a link). Landscape 16:10, at least 800×500</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Image file name (or a link). Landscape 16:10, at least 800×500</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">e.g. inkwell.png</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr" s="2">
+      <c r="F5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Card picture</t>
         </is>
@@ -703,22 +1004,27 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Shared</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Square logo/icon. At least 256×256. Used where a picture is too big</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Square icon, at least 256×256</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">e.g. inkwell-icon.png</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Small icon (search results, compact lists)</t>
+      <c r="F6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Small icon (compact lists)</t>
         </is>
       </c>
     </row>
@@ -730,20 +1036,25 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr" s="2">
+      <c r="D7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">What the image shows, for screen readers</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr" s="2">
+      <c r="E7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Free text</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr" s="2">
+      <c r="F7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Hidden alt text</t>
         </is>
@@ -757,22 +1068,27 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr" s="2">
+      <c r="D8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Youngest age it suits</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr" s="2">
+      <c r="E8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Whole number 3–14</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Parents "Age" filter and Teachers "Grade" filter (calculated)</t>
+      <c r="F8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents "Age" filter (worked out)</t>
         </is>
       </c>
     </row>
@@ -784,22 +1100,27 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr" s="2">
+      <c r="D9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Oldest age it suits</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr" s="2">
+      <c r="E9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Whole number 3–14</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Same as above</t>
+      <c r="F9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents "Age" filter (worked out)</t>
         </is>
       </c>
     </row>
@@ -811,22 +1132,27 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr" s="2">
+      <c r="D10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Typical play time for one round</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr" s="2">
+      <c r="E10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Whole number</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">"Minutes" filter (5 / 10 / 20) and the "10 min" badge</t>
+      <c r="F10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"10 min" badge, Teachers Minutes filter</t>
         </is>
       </c>
     </row>
@@ -838,22 +1164,27 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr" s="2">
+      <c r="D11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Who plays. Several allowed, separated by commas</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr" s="2">
+      <c r="E11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">See Lists tab</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Badge (e.g. Solo)</t>
+      <c r="F11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Badge; Parents "Together" filter</t>
         </is>
       </c>
     </row>
@@ -865,18 +1196,23 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="inlineStr" s="2">
+      <c r="D12" s="2"/>
+      <c r="E12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Free, Free with account, Paid</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">First badge on the card</t>
+      <c r="F12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">First badge</t>
         </is>
       </c>
     </row>
@@ -888,20 +1224,25 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Can it be played with no internet?</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Playable with no internet?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes / No</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr" s="2">
+      <c r="F13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">"Offline" badge</t>
         </is>
@@ -915,22 +1256,27 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr" s="2">
+      <c r="D14" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Can a non-reader play it?</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr" s="2">
+      <c r="E14" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Yes / No</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Parents "No reading needed" filter + badge</t>
+      <c r="F14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Badge; Parents "Also" filter</t>
         </is>
       </c>
     </row>
@@ -942,22 +1288,27 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">Shared</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Where it runs. Several allowed, separated by commas</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Where it runs, separated by commas</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">See Lists tab</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Not shown yet; kept for future filters</t>
+      <c r="F15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not shown yet</t>
         </is>
       </c>
     </row>
@@ -969,22 +1320,27 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr" s="2">
+      <c r="D16" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1–3 skills, separated by commas</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">See Lists tab (add new ones there)</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">"Builds …" line on the card</t>
+          <t xml:space="preserve">See Lists tab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Builds …" line</t>
         </is>
       </c>
     </row>
@@ -996,257 +1352,917 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Shared</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Does it feel like a game or like math?</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">A game or math?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">A game, Math</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">"Feels like" filter (both pages)</t>
+      <c r="F17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Feels like" filter</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">When (parents)</t>
+          <t xml:space="preserve">Partner</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">If on Parents</t>
+          <t xml:space="preserve">Shared</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">When families would play it. Several allowed, separated by commas</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">See Lists tab</t>
+          <t xml:space="preserve">Who makes it</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents "When" filter</t>
+          <t xml:space="preserve">Free text</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Not shown yet</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Teacher moments</t>
+          <t xml:space="preserve">Notes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">If on Teachers</t>
+          <t xml:space="preserve">Shared</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Which lesson moments it appears under. Several allowed, separated by commas</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">See Lists tab</t>
+          <t xml:space="preserve">For us only</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Teachers accordion</t>
+          <t xml:space="preserve">Free text</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Never shown</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Show on</t>
+          <t xml:space="preserve">On Teachers page</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Teachers</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Which page(s) list it</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Both, Teachers, Parents</t>
+          <t xml:space="preserve">List it on the Teachers page?</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Which page it appears on</t>
+          <t xml:space="preserve">Yes / No</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teachers page</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Partner</t>
+          <t xml:space="preserve">Teacher grades</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Teachers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Who makes it</t>
+          <t xml:space="preserve">If on Teachers</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Free text</t>
+          <t xml:space="preserve">Grades it suits (set by hand), separated by commas</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown yet</t>
+          <t xml:space="preserve">K-1, 2-3, 4-5</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teachers "Grade" filter</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Featured</t>
+          <t xml:space="preserve">Teacher moments</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Teachers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pin to the top of the list</t>
+          <t xml:space="preserve">If on Teachers</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Yes / No</t>
+          <t xml:space="preserve">Moments it appears under, separated by commas. Row order sets the starting order inside each moment</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Order on the page</t>
+          <t xml:space="preserve">See Lists tab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teachers accordion</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Notes</t>
+          <t xml:space="preserve">Teacher URL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Teachers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Anything for us, not shown on the site</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Only if teachers should go somewhere else</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Full link</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Open game" on Teachers</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teacher subtitle</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teachers</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if different for teachers</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Free text</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Never shown</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2"/>
-      <c r="B24" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="F24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Line under the name</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">How filters are worked out</t>
-        </is>
-      </c>
-      <c r="B25" s="2"/>
+          <t xml:space="preserve">Teacher image file</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teachers</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Teachers "Grade" comes from the age range: K-1 = ages 5–7, 2-3 = ages 7–9, 4-5 = ages 9–11. Parents "Age" (4-5, 6-8, 9-11) also comes from the age range. A game shows under every group its range overlaps.</t>
-        </is>
-      </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if different for teachers</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">File name or link</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Card picture</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Badges on the card</t>
-        </is>
-      </c>
-      <c r="B26" s="2"/>
+          <t xml:space="preserve">Teacher icon file</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teachers</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Generated automatically from Cost, Players, Minutes, Works offline and No reading needed, so they always match the filters.</t>
-        </is>
-      </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if different for teachers</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">File name or link</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Small icon</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Images</t>
-        </is>
-      </c>
-      <c r="B27" s="2"/>
+          <t xml:space="preserve">Teacher minutes</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teachers</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send the image files in one folder with this sheet. File names must match the "Image file" / "Icon file" columns exactly.</t>
-        </is>
-      </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if a class round is a different length</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Whole number</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Badge and Minutes filter</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">Teacher skills</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teachers</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if different for teachers</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">See Lists tab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Builds …" line</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teacher feels like</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teachers</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if different for teachers</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A game, Math</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Feels like" filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teacher badges</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teachers</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Which badges to show. Blank = all</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">See Lists tab → Badges</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Badges on the card</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teacher featured</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teachers</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Show first in Teachers search results</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Yes / No</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Search order</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">On Parents page</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">List it in the Parents Library?</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Yes / No</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents page</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">When (parents)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">If on Parents</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">When families play it, separated by commas</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">See Lists tab</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents "When" filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parent URL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if parents should go somewhere else</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Full link</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Play" on Parents</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parent subtitle</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if different for parents</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Free text</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Line under the name</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parent image file</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if different for parents</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">File name or link</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Card picture</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parent icon file</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if different for parents</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">File name or link</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Small icon</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parent minutes</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if different at home</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Whole number</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Badge</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parent skills</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if different for parents</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">See Lists tab</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Builds …" line</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parent feels like</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only if different for parents</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A game, Math</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">"Feels like" filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parent badges</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Which badges to show. Blank = all</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">See Lists tab → Badges</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Badges on the card</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parent featured</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Pin to the top of the Library</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Yes / No</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Library order</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">How sections work</t>
+        </is>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Shared columns (dark headers) apply to both pages. Teachers columns (blue) and Parents columns (green) only change that page. Leave an "only if different" column blank to use the Shared value.</t>
+        </is>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Filters</t>
+        </is>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Teachers "Grade" is set by hand in Teacher grades. Parents "Age" (4-5, 6-8, 9-11) is worked out from Age from / Age to. Minutes filter uses Teacher minutes if filled, else Minutes.</t>
+        </is>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Moment order</t>
+        </is>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A new game is added to the end of each moment it lists. After import, reorder games inside a moment by dragging in Studio. Re-importing never reorders existing games.</t>
+        </is>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Images</t>
+        </is>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Send the images in one folder with this sheet. File names must match exactly. Override images reuse the Shared image description; edit alt text in Studio if it should differ.</t>
+        </is>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Comma columns</t>
         </is>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">For Players, Platforms, Skills, When and Teacher moments, use values from the Lists tab, separated by commas. Spelling must match.</t>
-        </is>
-      </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Use values from the Lists tab, separated by commas. Spelling must match (case doesn't).</t>
+        </is>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1256,11 +2272,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1271,22 +2289,32 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Teacher grades</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Teacher moments</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">When (parents)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Players</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Platforms</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Badges</t>
         </is>
       </c>
     </row>
@@ -1298,22 +2326,32 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">K-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Morning warm-up</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="2">
+      <c r="D2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Car or waiting</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="2">
+      <c r="E2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Solo</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr" s="2">
+      <c r="F2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Web</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Cost</t>
         </is>
       </c>
     </row>
@@ -1325,22 +2363,32 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2-3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Early finishers</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr" s="2">
+      <c r="D3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Free time</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr" s="2">
+      <c r="E3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Pairs</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr" s="2">
+      <c r="F3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">iOS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Players</t>
         </is>
       </c>
     </row>
@@ -1352,22 +2400,32 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">4-5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Indoor recess</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr" s="2">
+      <c r="D4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Weekend</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr" s="2">
+      <c r="E4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Small group</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr" s="2">
+      <c r="F4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Android</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Minutes</t>
         </is>
       </c>
     </row>
@@ -1377,20 +2435,26 @@
           <t xml:space="preserve">Spatial reasoning</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr" s="2">
+      <c r="B5" s="2"/>
+      <c r="C5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">The last 10 minutes</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" t="inlineStr" s="2">
+      <c r="D5" s="2"/>
+      <c r="E5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Whole class</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr" s="2">
+      <c r="F5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Print</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Offline</t>
         </is>
       </c>
     </row>
@@ -1400,16 +2464,22 @@
           <t xml:space="preserve">Sequencing</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="2">
+      <c r="B6" s="2"/>
+      <c r="C6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Cover or sub day</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" t="inlineStr" s="2">
+      <c r="E6" s="2"/>
+      <c r="F6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Physical game</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No reading needed</t>
         </is>
       </c>
     </row>
@@ -1419,14 +2489,16 @@
           <t xml:space="preserve">Working memory</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr" s="2">
+      <c r="B7" s="2"/>
+      <c r="C7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Friday reward time</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
@@ -1438,6 +2510,8 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
@@ -1449,6 +2523,8 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
@@ -1460,6 +2536,8 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
@@ -1471,6 +2549,8 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2"/>
@@ -1478,17 +2558,21 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Add new values at the bottom of a column. New skills, moments and "When" options become filter options automatically.</t>
+          <t xml:space="preserve">Add new skills, moments or "When" options at the bottom of a column. They become filter options automatically.</t>
         </is>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/scripts/games-template.xlsx
+++ b/scripts/games-template.xlsx
@@ -778,9 +778,8 @@
       <formula1>3</formula1>
       <formula2>14</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Enter a whole number from 1 to 120" sqref="I2:I500">
-      <formula1>1</formula1>
-      <formula2>120</formula2>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: 5, 10, 20, 30+" sqref="I2:I500">
+      <formula1>"5,10,20,30+"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Free, Free with account, Paid" sqref="K2:K500">
       <formula1>"Free,Free with account,Paid"</formula1>
@@ -797,9 +796,8 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Yes, No" sqref="S2:S500">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Enter a whole number from 1 to 120" sqref="Z2:Z500">
-      <formula1>1</formula1>
-      <formula2>120</formula2>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: 5, 10, 20, 30+" sqref="Z2:Z500">
+      <formula1>"5,10,20,30+"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: A game, Math" sqref="AB2:AB500">
       <formula1>"A game,Math"</formula1>
@@ -810,9 +808,8 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Yes, No" sqref="AE2:AE500">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Enter a whole number from 1 to 120" sqref="AK2:AK500">
-      <formula1>1</formula1>
-      <formula2>120</formula2>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: 5, 10, 20, 30+" sqref="AK2:AK500">
+      <formula1>"5,10,20,30+"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: A game, Math" sqref="AM2:AM500">
       <formula1>"A game,Math"</formula1>
@@ -1145,9 +1142,9 @@
           <t xml:space="preserve">Typical play time for one round</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Whole number</t>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5, 10, 20 or 30+</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="2">
@@ -1685,9 +1682,9 @@
           <t xml:space="preserve">Only if a class round is a different length</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Whole number</t>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5, 10, 20 or 30+</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="2">
@@ -2037,9 +2034,9 @@
           <t xml:space="preserve">Only if different at home</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Whole number</t>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5, 10, 20 or 30+</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="2">
